--- a/Assignm3.xlsx
+++ b/Assignm3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DWNLD\Раз\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\PycharmProjects\WelcomeScreen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C2115-B8AF-47E2-890A-070DFCB82B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5157BB-2EE2-4BC3-B90F-655CE0CE6FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="1080" windowWidth="21855" windowHeight="19800" xr2:uid="{252D3175-C7D1-45E7-840F-45C8B420D725}"/>
+    <workbookView xWindow="4290" yWindow="1800" windowWidth="21855" windowHeight="19800" xr2:uid="{252D3175-C7D1-45E7-840F-45C8B420D725}"/>
   </bookViews>
   <sheets>
     <sheet name="Достижения" sheetId="1" r:id="rId1"/>
@@ -884,7 +884,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>4</v>
@@ -898,7 +898,7 @@
         <v>92</v>
       </c>
       <c r="B3" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2">
         <v>4</v>
@@ -912,7 +912,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2">
         <v>6</v>
@@ -926,7 +926,7 @@
         <v>133</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>2</v>
@@ -940,7 +940,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -954,7 +954,7 @@
         <v>127</v>
       </c>
       <c r="B7" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -968,7 +968,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2">
         <v>4</v>
@@ -982,7 +982,7 @@
         <v>83</v>
       </c>
       <c r="B9" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2">
         <v>7</v>
@@ -996,7 +996,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2">
         <v>3</v>
@@ -1010,7 +1010,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2">
         <v>5</v>
@@ -1024,7 +1024,7 @@
         <v>79</v>
       </c>
       <c r="B12" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2">
         <v>6</v>
@@ -1038,7 +1038,7 @@
         <v>77</v>
       </c>
       <c r="B13" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
         <v>6</v>
@@ -1052,7 +1052,7 @@
         <v>58</v>
       </c>
       <c r="B14" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -1066,7 +1066,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2">
         <v>5</v>
@@ -1080,7 +1080,7 @@
         <v>125</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -1094,7 +1094,7 @@
         <v>110</v>
       </c>
       <c r="B17" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C18" s="2">
         <v>6</v>
@@ -1122,7 +1122,7 @@
         <v>124</v>
       </c>
       <c r="B19" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2">
         <v>4</v>
@@ -1136,7 +1136,7 @@
         <v>130</v>
       </c>
       <c r="B20" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2">
         <v>7</v>
@@ -1150,7 +1150,7 @@
         <v>114</v>
       </c>
       <c r="B21" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2">
         <v>2</v>
@@ -1164,7 +1164,7 @@
         <v>70</v>
       </c>
       <c r="B22" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C22" s="2">
         <v>6</v>
@@ -1178,7 +1178,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C23" s="2">
         <v>6</v>
@@ -1192,7 +1192,7 @@
         <v>40</v>
       </c>
       <c r="B24" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
@@ -1206,7 +1206,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C25" s="2">
         <v>7</v>
@@ -1220,7 +1220,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
@@ -1234,7 +1234,7 @@
         <v>72</v>
       </c>
       <c r="B27" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2">
         <v>2</v>
@@ -1248,7 +1248,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>112</v>
       </c>
       <c r="B29" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>61</v>
       </c>
       <c r="B30" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C30" s="2">
         <v>3</v>
@@ -1290,7 +1290,7 @@
         <v>74</v>
       </c>
       <c r="B31" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2">
         <v>7</v>
@@ -1304,7 +1304,7 @@
         <v>90</v>
       </c>
       <c r="B32" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2">
         <v>4</v>
@@ -1318,7 +1318,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2">
         <v>2</v>
@@ -1332,7 +1332,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>118</v>
       </c>
       <c r="B35" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C35" s="2">
         <v>4</v>
@@ -1360,7 +1360,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C36" s="2">
         <v>2</v>
@@ -1374,7 +1374,7 @@
         <v>94</v>
       </c>
       <c r="B37" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C37" s="2">
         <v>4</v>
@@ -1388,7 +1388,7 @@
         <v>132</v>
       </c>
       <c r="B38" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2">
         <v>5</v>
@@ -1416,7 +1416,7 @@
         <v>51</v>
       </c>
       <c r="B40" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C40" s="2">
         <v>2</v>
@@ -1430,7 +1430,7 @@
         <v>49</v>
       </c>
       <c r="B41" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
@@ -1444,7 +1444,7 @@
         <v>37</v>
       </c>
       <c r="B42" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>113</v>
       </c>
       <c r="B43" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2">
         <v>4</v>
@@ -1472,7 +1472,7 @@
         <v>24</v>
       </c>
       <c r="B44" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C44" s="2">
         <v>5</v>
@@ -1486,7 +1486,7 @@
         <v>100</v>
       </c>
       <c r="B45" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2">
         <v>4</v>
@@ -1500,7 +1500,7 @@
         <v>123</v>
       </c>
       <c r="B46" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1514,7 +1514,7 @@
         <v>122</v>
       </c>
       <c r="B47" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C47" s="2">
         <v>7</v>
@@ -1528,7 +1528,7 @@
         <v>104</v>
       </c>
       <c r="B48" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C48" s="2">
         <v>4</v>
@@ -1542,7 +1542,7 @@
         <v>134</v>
       </c>
       <c r="B49" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2">
         <v>5</v>
@@ -1556,7 +1556,7 @@
         <v>54</v>
       </c>
       <c r="B50" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C50" s="2">
         <v>3</v>
@@ -1570,7 +1570,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2">
         <v>2</v>
@@ -1584,7 +1584,7 @@
         <v>30</v>
       </c>
       <c r="B52" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>66</v>
       </c>
       <c r="B53" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -1612,7 +1612,7 @@
         <v>81</v>
       </c>
       <c r="B54" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2">
         <v>6</v>
@@ -1626,7 +1626,7 @@
         <v>32</v>
       </c>
       <c r="B55" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -1654,7 +1654,7 @@
         <v>36</v>
       </c>
       <c r="B57" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C57" s="2">
         <v>5</v>
@@ -1668,7 +1668,7 @@
         <v>42</v>
       </c>
       <c r="B58" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2">
         <v>6</v>
@@ -1682,7 +1682,7 @@
         <v>98</v>
       </c>
       <c r="B59" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C59" s="2">
         <v>4</v>
@@ -1696,7 +1696,7 @@
         <v>106</v>
       </c>
       <c r="B60" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2">
         <v>4</v>
@@ -1710,7 +1710,7 @@
         <v>107</v>
       </c>
       <c r="B61" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C61" s="2">
         <v>4</v>
@@ -1724,7 +1724,7 @@
         <v>117</v>
       </c>
       <c r="B62" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2">
         <v>7</v>
@@ -1738,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2">
         <v>5</v>
@@ -1752,7 +1752,7 @@
         <v>71</v>
       </c>
       <c r="B64" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C64" s="2">
         <v>7</v>
@@ -1766,7 +1766,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>102</v>
       </c>
       <c r="B66" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>128</v>
       </c>
       <c r="B67" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C67" s="2">
         <v>5</v>
@@ -1808,7 +1808,7 @@
         <v>91</v>
       </c>
       <c r="B68" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2">
         <v>2</v>
@@ -1822,7 +1822,7 @@
         <v>87</v>
       </c>
       <c r="B69" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C70" s="2">
         <v>3</v>
@@ -1850,7 +1850,7 @@
         <v>15</v>
       </c>
       <c r="B71" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2">
         <v>6</v>
@@ -1864,7 +1864,7 @@
         <v>103</v>
       </c>
       <c r="B72" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -1878,7 +1878,7 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2">
         <v>3</v>
@@ -1892,7 +1892,7 @@
         <v>82</v>
       </c>
       <c r="B74" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C74" s="2">
         <v>7</v>
@@ -1906,7 +1906,7 @@
         <v>64</v>
       </c>
       <c r="B75" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C75" s="2">
         <v>6</v>
@@ -1920,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="B76" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2">
         <v>7</v>
@@ -1934,7 +1934,7 @@
         <v>13</v>
       </c>
       <c r="B77" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>45</v>
       </c>
       <c r="B78" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>96</v>
       </c>
       <c r="B79" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C79" s="2">
         <v>2</v>
@@ -1976,7 +1976,7 @@
         <v>121</v>
       </c>
       <c r="B80" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2">
         <v>3</v>
@@ -1990,7 +1990,7 @@
         <v>120</v>
       </c>
       <c r="B81" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2">
         <v>3</v>
@@ -2004,7 +2004,7 @@
         <v>59</v>
       </c>
       <c r="B82" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2">
         <v>7</v>
@@ -2018,7 +2018,7 @@
         <v>131</v>
       </c>
       <c r="B83" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C83" s="2">
         <v>6</v>
@@ -2032,7 +2032,7 @@
         <v>21</v>
       </c>
       <c r="B84" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2">
         <v>3</v>
@@ -2046,7 +2046,7 @@
         <v>105</v>
       </c>
       <c r="B85" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C85" s="2">
         <v>4</v>
@@ -2060,7 +2060,7 @@
         <v>35</v>
       </c>
       <c r="B86" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C86" s="2">
         <v>4</v>
@@ -2074,7 +2074,7 @@
         <v>5</v>
       </c>
       <c r="B87" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
@@ -2088,7 +2088,7 @@
         <v>80</v>
       </c>
       <c r="B88" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C88" s="2">
         <v>4</v>
@@ -2102,7 +2102,7 @@
         <v>136</v>
       </c>
       <c r="B89" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C89" s="2">
         <v>7</v>
@@ -2116,7 +2116,7 @@
         <v>119</v>
       </c>
       <c r="B90" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C90" s="2">
         <v>4</v>
@@ -2130,7 +2130,7 @@
         <v>68</v>
       </c>
       <c r="B91" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C91" s="2">
         <v>4</v>
@@ -2144,7 +2144,7 @@
         <v>126</v>
       </c>
       <c r="B92" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C92" s="2">
         <v>6</v>
@@ -2158,7 +2158,7 @@
         <v>129</v>
       </c>
       <c r="B93" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2">
         <v>7</v>
@@ -2172,7 +2172,7 @@
         <v>116</v>
       </c>
       <c r="B94" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C94" s="2">
         <v>4</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="B95" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C95" s="2">
         <v>5</v>
@@ -2200,7 +2200,7 @@
         <v>75</v>
       </c>
       <c r="B96" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2">
         <v>7</v>
@@ -2214,7 +2214,7 @@
         <v>2</v>
       </c>
       <c r="B97" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C97" s="2">
         <v>6</v>
@@ -2228,7 +2228,7 @@
         <v>46</v>
       </c>
       <c r="B98" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2">
         <v>2</v>
@@ -2242,7 +2242,7 @@
         <v>88</v>
       </c>
       <c r="B99" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C99" s="2">
         <v>4</v>
@@ -2256,7 +2256,7 @@
         <v>73</v>
       </c>
       <c r="B100" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C100" s="2">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         <v>16</v>
       </c>
       <c r="B101" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>138</v>
       </c>
       <c r="B102" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C102" s="2">
         <v>5</v>
@@ -2298,7 +2298,7 @@
         <v>69</v>
       </c>
       <c r="B103" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C103" s="2">
         <v>3</v>
@@ -2312,7 +2312,7 @@
         <v>33</v>
       </c>
       <c r="B104" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C104" s="2">
         <v>3</v>
@@ -2326,7 +2326,7 @@
         <v>44</v>
       </c>
       <c r="B105" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C105" s="2">
         <v>4</v>
@@ -2340,7 +2340,7 @@
         <v>60</v>
       </c>
       <c r="B106" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2">
         <v>5</v>
@@ -2354,7 +2354,7 @@
         <v>55</v>
       </c>
       <c r="B107" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C107" s="2">
         <v>2</v>
@@ -2368,7 +2368,7 @@
         <v>99</v>
       </c>
       <c r="B108" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C108" s="2">
         <v>5</v>
@@ -2382,7 +2382,7 @@
         <v>76</v>
       </c>
       <c r="B109" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C109" s="2">
         <v>2</v>
@@ -2396,7 +2396,7 @@
         <v>31</v>
       </c>
       <c r="B110" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C110" s="2">
         <v>5</v>
@@ -2410,7 +2410,7 @@
         <v>43</v>
       </c>
       <c r="B111" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2">
         <v>6</v>
@@ -2424,7 +2424,7 @@
         <v>56</v>
       </c>
       <c r="B112" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C112" s="2">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>19</v>
       </c>
       <c r="B113" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C113" s="2">
         <v>2</v>
@@ -2452,7 +2452,7 @@
         <v>34</v>
       </c>
       <c r="B114" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C114" s="2">
         <v>3</v>
@@ -2466,7 +2466,7 @@
         <v>20</v>
       </c>
       <c r="B115" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C115" s="2">
         <v>3</v>
@@ -2480,7 +2480,7 @@
         <v>95</v>
       </c>
       <c r="B116" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>101</v>
       </c>
       <c r="B117" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2">
         <v>5</v>
@@ -2508,7 +2508,7 @@
         <v>137</v>
       </c>
       <c r="B118" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C118" s="2">
         <v>4</v>
@@ -2522,7 +2522,7 @@
         <v>48</v>
       </c>
       <c r="B119" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C119" s="2">
         <v>4</v>
@@ -2536,7 +2536,7 @@
         <v>108</v>
       </c>
       <c r="B120" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C120" s="2">
         <v>5</v>
@@ -2550,7 +2550,7 @@
         <v>53</v>
       </c>
       <c r="B121" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C121" s="2">
         <v>6</v>
@@ -2564,7 +2564,7 @@
         <v>78</v>
       </c>
       <c r="B122" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -2578,7 +2578,7 @@
         <v>140</v>
       </c>
       <c r="B123" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C123" s="2">
         <v>3</v>
@@ -2592,7 +2592,7 @@
         <v>14</v>
       </c>
       <c r="B124" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2">
         <v>6</v>
@@ -2606,7 +2606,7 @@
         <v>89</v>
       </c>
       <c r="B125" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
@@ -2620,7 +2620,7 @@
         <v>109</v>
       </c>
       <c r="B126" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C126" s="2">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>23</v>
       </c>
       <c r="B127" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C127" s="2">
         <v>7</v>
@@ -2648,7 +2648,7 @@
         <v>6</v>
       </c>
       <c r="B128" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C128" s="2">
         <v>5</v>
@@ -2662,7 +2662,7 @@
         <v>27</v>
       </c>
       <c r="B129" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C129" s="2">
         <v>7</v>
@@ -2676,7 +2676,7 @@
         <v>17</v>
       </c>
       <c r="B130" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C130" s="2">
         <v>6</v>
@@ -2690,7 +2690,7 @@
         <v>47</v>
       </c>
       <c r="B131" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         <v>85</v>
       </c>
       <c r="B132" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C132" s="2">
         <v>3</v>
@@ -2718,7 +2718,7 @@
         <v>84</v>
       </c>
       <c r="B133" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C133" s="2">
         <v>1</v>
@@ -2732,7 +2732,7 @@
         <v>93</v>
       </c>
       <c r="B134" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>65</v>
       </c>
       <c r="B135" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C135" s="2">
         <v>2</v>
@@ -2760,7 +2760,7 @@
         <v>12</v>
       </c>
       <c r="B136" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
@@ -2774,7 +2774,7 @@
         <v>62</v>
       </c>
       <c r="B137" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C137" s="2">
         <v>3</v>
@@ -2788,7 +2788,7 @@
         <v>111</v>
       </c>
       <c r="B138" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C138" s="2">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>97</v>
       </c>
       <c r="B139" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C139" s="2">
         <v>6</v>
@@ -2816,7 +2816,7 @@
         <v>135</v>
       </c>
       <c r="B140" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C140" s="2">
         <v>6</v>
@@ -2830,7 +2830,7 @@
         <v>57</v>
       </c>
       <c r="B141" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C141" s="2">
         <v>3</v>
@@ -2844,7 +2844,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C142" s="2">
         <v>3</v>
@@ -2858,7 +2858,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
@@ -2872,7 +2872,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
